--- a/VERGARA/Junio/vergara JUNIO.xlsx
+++ b/VERGARA/Junio/vergara JUNIO.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF59CF6-A62A-4F48-9CD6-A7424821CBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BA86C-A02A-42B9-A5BB-3DE092A8AEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="anotaciones" sheetId="3" r:id="rId3"/>
+    <sheet name="anotaciones " sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$Q$101</definedName>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="295">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -626,9 +626,6 @@
     <t>10°D</t>
   </si>
   <si>
-    <t>Agustina Malfigliaccio y Alan Pons</t>
-  </si>
-  <si>
     <t>11°A</t>
   </si>
   <si>
@@ -901,6 +898,21 @@
   </si>
   <si>
     <t>Zaffalon Veronica - Compra de bomba pozo napa nieva vazzer</t>
+  </si>
+  <si>
+    <t>Luz Maria Alberio</t>
+  </si>
+  <si>
+    <t>hay que agregar a luzalberio@gmail.com  a la cadena, es nueva inquilina del 10D</t>
+  </si>
+  <si>
+    <t>PABLO PLEBS TIENE UNA TRANSFERENCIA DE $91.922,35 EN ABRIL QUE NO SE LA IMPUTAMOS NUNCA (NI COMO TRANSF NO IDENTIDICADA) POR ENDE NO DEBE TENER DEUDA ALGUNA - ES MAS, SEGÚN ROMI EL PAGO (ESTE MES, EN JUNIO) 119 MIL Y PICO, POR ENDE LE DEBE QUEDAR DINERO A FAVOR</t>
+  </si>
+  <si>
+    <t>QUE QUEDE SIN DEUDA</t>
+  </si>
+  <si>
+    <t>el mes pasado quedo debiendo 5,300$ cuando es incorrecto, debe quedar sin deuda (si es que este mes abono)</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1176,6 +1188,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1545,7 +1581,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1818,20 +1854,36 @@
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="20" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1839,50 +1891,12 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="24" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1890,25 +1904,54 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="20" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2273,12 +2316,12 @@
       <c r="A5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="202" t="s">
-        <v>280</v>
-      </c>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="201"/>
+      <c r="B5" s="193" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="194"/>
+      <c r="D5" s="194"/>
+      <c r="E5" s="195"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
@@ -2292,49 +2335,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="203" t="s">
+      <c r="B8" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="193"/>
+      <c r="C8" s="197"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="193"/>
-      <c r="C9" s="193"/>
+      <c r="B9" s="197"/>
+      <c r="C9" s="197"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="193"/>
-      <c r="C10" s="193"/>
+      <c r="B10" s="197"/>
+      <c r="C10" s="197"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="204" t="s">
+      <c r="A13" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="193"/>
-      <c r="C13" s="193"/>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
+      <c r="B13" s="197"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="193"/>
+      <c r="A14" s="197"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="193"/>
+      <c r="A15" s="197"/>
+      <c r="B15" s="197"/>
+      <c r="C15" s="197"/>
+      <c r="D15" s="197"/>
+      <c r="E15" s="197"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-      <c r="E16" s="193"/>
+      <c r="A16" s="197"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2430,23 +2473,23 @@
       <c r="E27" s="93"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="194" t="s">
-        <v>281</v>
-      </c>
-      <c r="B28" s="195"/>
+      <c r="A28" s="199" t="s">
+        <v>280</v>
+      </c>
+      <c r="B28" s="200"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="222">
+      <c r="D28" s="190">
         <v>35000</v>
       </c>
       <c r="E28" s="94" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="194" t="s">
-        <v>283</v>
-      </c>
-      <c r="B29" s="195"/>
+      <c r="A29" s="199" t="s">
+        <v>282</v>
+      </c>
+      <c r="B29" s="200"/>
       <c r="C29" s="5"/>
       <c r="D29" s="184">
         <v>470000</v>
@@ -2489,10 +2532,10 @@
       <c r="G32" s="159"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="194" t="s">
+      <c r="A33" s="199" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="195"/>
+      <c r="B33" s="200"/>
       <c r="C33" s="54"/>
       <c r="D33" s="117">
         <v>719.9</v>
@@ -2536,7 +2579,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>28</v>
@@ -2610,7 +2653,7 @@
       </c>
       <c r="B42" s="53"/>
       <c r="C42" s="53"/>
-      <c r="D42" s="227">
+      <c r="D42" s="191">
         <v>84629.46</v>
       </c>
       <c r="E42" s="103"/>
@@ -2629,10 +2672,10 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="194" t="s">
+      <c r="A44" s="199" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="195"/>
+      <c r="B44" s="200"/>
       <c r="C44" s="5"/>
       <c r="D44" s="117">
         <v>81423.929999999993</v>
@@ -2663,10 +2706,10 @@
       <c r="E46" s="99"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="196" t="s">
+      <c r="A47" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="197"/>
+      <c r="B47" s="205"/>
       <c r="C47" s="65"/>
       <c r="D47" s="117">
         <v>84500</v>
@@ -2676,10 +2719,10 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="196" t="s">
+      <c r="A48" s="204" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="197"/>
+      <c r="B48" s="205"/>
       <c r="C48" s="65"/>
       <c r="D48" s="117">
         <v>262099.86</v>
@@ -2716,10 +2759,10 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="194" t="s">
+      <c r="A51" s="199" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="195"/>
+      <c r="B51" s="200"/>
       <c r="C51" s="55"/>
       <c r="D51" s="117">
         <v>165000</v>
@@ -2729,25 +2772,25 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="223" t="s">
+      <c r="A52" s="207" t="s">
+        <v>284</v>
+      </c>
+      <c r="B52" s="208"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="191">
+        <v>110000</v>
+      </c>
+      <c r="E52" s="157" t="s">
         <v>285</v>
       </c>
-      <c r="B52" s="224"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="227">
-        <v>110000</v>
-      </c>
-      <c r="E52" s="157" t="s">
-        <v>286</v>
-      </c>
     </row>
     <row r="53" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="194" t="s">
-        <v>290</v>
-      </c>
-      <c r="B53" s="195"/>
+      <c r="A53" s="199" t="s">
+        <v>289</v>
+      </c>
+      <c r="B53" s="200"/>
       <c r="C53" s="55"/>
-      <c r="D53" s="227">
+      <c r="D53" s="191">
         <v>135000</v>
       </c>
       <c r="E53" s="157" t="s">
@@ -2768,10 +2811,10 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="194" t="s">
+      <c r="A55" s="199" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="195"/>
+      <c r="B55" s="200"/>
       <c r="C55" s="55"/>
       <c r="D55" s="117">
         <v>135000</v>
@@ -2782,44 +2825,44 @@
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="143" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B56" s="132"/>
       <c r="C56" s="55"/>
-      <c r="D56" s="227">
+      <c r="D56" s="191">
         <v>25000</v>
       </c>
       <c r="E56" s="157" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="225" t="s">
+      <c r="A57" s="202" t="s">
         <v>52</v>
       </c>
-      <c r="B57" s="226"/>
+      <c r="B57" s="203"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="227">
+      <c r="D57" s="191">
         <v>110000</v>
       </c>
       <c r="E57" s="158" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="199" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="194" t="s">
-        <v>287</v>
-      </c>
-      <c r="B58" s="195"/>
+      <c r="B58" s="200"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="228">
+      <c r="D58" s="192">
         <v>51150</v>
       </c>
       <c r="E58" s="157" t="s">
         <v>53</v>
       </c>
-      <c r="I58" s="194"/>
-      <c r="J58" s="195"/>
+      <c r="I58" s="199"/>
+      <c r="J58" s="200"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
@@ -2931,10 +2974,10 @@
       <c r="E70" s="115"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="194" t="s">
+      <c r="A71" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="195"/>
+      <c r="B71" s="200"/>
       <c r="C71" s="5"/>
       <c r="D71" s="101">
         <v>304993.06</v>
@@ -2963,12 +3006,12 @@
     <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:7" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="199" t="s">
+      <c r="A76" s="209" t="s">
         <v>63</v>
       </c>
-      <c r="B76" s="200"/>
-      <c r="C76" s="200"/>
-      <c r="D76" s="201"/>
+      <c r="B76" s="194"/>
+      <c r="C76" s="194"/>
+      <c r="D76" s="195"/>
       <c r="E76" s="150"/>
     </row>
     <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3152,16 +3195,16 @@
       <c r="F98" s="128"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="198" t="s">
+      <c r="A99" s="206" t="s">
         <v>80</v>
       </c>
-      <c r="B99" s="193"/>
-      <c r="C99" s="193"/>
+      <c r="B99" s="197"/>
+      <c r="C99" s="197"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="193"/>
-      <c r="B100" s="193"/>
-      <c r="C100" s="193"/>
+      <c r="A100" s="197"/>
+      <c r="B100" s="197"/>
+      <c r="C100" s="197"/>
     </row>
     <row r="101" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="54"/>
@@ -3196,40 +3239,35 @@
       <c r="M105" s="8"/>
     </row>
     <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="192"/>
-      <c r="B106" s="193"/>
-      <c r="C106" s="193"/>
-      <c r="D106" s="193"/>
-      <c r="E106" s="193"/>
+      <c r="A106" s="201"/>
+      <c r="B106" s="197"/>
+      <c r="C106" s="197"/>
+      <c r="D106" s="197"/>
+      <c r="E106" s="197"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="193"/>
-      <c r="B107" s="193"/>
-      <c r="C107" s="193"/>
-      <c r="D107" s="193"/>
-      <c r="E107" s="193"/>
+      <c r="A107" s="197"/>
+      <c r="B107" s="197"/>
+      <c r="C107" s="197"/>
+      <c r="D107" s="197"/>
+      <c r="E107" s="197"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="193"/>
-      <c r="B108" s="193"/>
-      <c r="C108" s="193"/>
-      <c r="D108" s="193"/>
-      <c r="E108" s="193"/>
+      <c r="A108" s="197"/>
+      <c r="B108" s="197"/>
+      <c r="C108" s="197"/>
+      <c r="D108" s="197"/>
+      <c r="E108" s="197"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="193"/>
-      <c r="B109" s="193"/>
-      <c r="C109" s="193"/>
-      <c r="D109" s="193"/>
-      <c r="E109" s="193"/>
+      <c r="A109" s="197"/>
+      <c r="B109" s="197"/>
+      <c r="C109" s="197"/>
+      <c r="D109" s="197"/>
+      <c r="E109" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A106:E109"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="A55:B55"/>
@@ -3245,6 +3283,11 @@
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A58:B58"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3282,10 +3325,10 @@
       <c r="E1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="220">
+      <c r="F1" s="214">
         <v>1241030.1599999999</v>
       </c>
-      <c r="G1" s="221"/>
+      <c r="G1" s="215"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3293,16 +3336,16 @@
         <v>82</v>
       </c>
       <c r="L1" s="6"/>
-      <c r="M1" s="219">
+      <c r="M1" s="211">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="193"/>
+      <c r="N1" s="197"/>
       <c r="O1" s="144"/>
-      <c r="P1" s="218">
+      <c r="P1" s="210">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="193"/>
+      <c r="Q1" s="197"/>
       <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3313,103 +3356,103 @@
       <c r="E2" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="229">
+      <c r="F2" s="225">
         <v>561462.80000000005</v>
       </c>
-      <c r="G2" s="230"/>
+      <c r="G2" s="226"/>
       <c r="H2" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="217">
+      <c r="I2" s="212">
         <v>1200000</v>
       </c>
-      <c r="J2" s="205"/>
+      <c r="J2" s="213"/>
       <c r="K2" s="6" t="s">
         <v>85</v>
       </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="217">
+      <c r="M2" s="212">
         <v>304993.06</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="213"/>
       <c r="O2" s="146"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="205"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="213"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="212" t="s">
+      <c r="A3" s="216" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="122"/>
-      <c r="C3" s="206" t="s">
+      <c r="C3" s="222" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="206" t="s">
+      <c r="D3" s="222" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="211" t="s">
+      <c r="E3" s="228" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="206" t="s">
+      <c r="F3" s="222" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="208" t="s">
+      <c r="G3" s="218" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="206" t="s">
+      <c r="H3" s="222" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="214" t="s">
+      <c r="I3" s="220" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="208" t="s">
+      <c r="J3" s="218" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="210" t="str">
+      <c r="K3" s="227" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="208" t="s">
+      <c r="L3" s="218" t="s">
         <v>94</v>
       </c>
-      <c r="M3" s="208" t="s">
+      <c r="M3" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="N3" s="208" t="s">
+      <c r="N3" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="O3" s="208" t="s">
+      <c r="O3" s="218" t="s">
         <v>97</v>
       </c>
       <c r="P3" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="Q3" s="216" t="s">
+      <c r="Q3" s="224" t="s">
         <v>99</v>
       </c>
       <c r="T3" s="45"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="213"/>
+      <c r="A4" s="217"/>
       <c r="B4" s="123"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="209"/>
-      <c r="M4" s="209"/>
-      <c r="N4" s="209"/>
-      <c r="O4" s="209"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="219"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="219"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="219"/>
+      <c r="J4" s="219"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="219"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
       <c r="P4" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="Q4" s="207"/>
+      <c r="Q4" s="223"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
@@ -3558,7 +3601,7 @@
       <c r="G7" s="72">
         <v>203142.35</v>
       </c>
-      <c r="H7" s="124">
+      <c r="H7" s="229">
         <v>108461</v>
       </c>
       <c r="I7" s="73">
@@ -5481,7 +5524,7 @@
       <c r="G36" s="72">
         <v>88536.639999999999</v>
       </c>
-      <c r="H36" s="191">
+      <c r="H36" s="189">
         <f>150000</f>
         <v>150000</v>
       </c>
@@ -6002,8 +6045,8 @@
       <c r="D44" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="E44" s="61" t="s">
-        <v>199</v>
+      <c r="E44" s="230" t="s">
+        <v>290</v>
       </c>
       <c r="F44" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6058,16 +6101,16 @@
         <v>3</v>
       </c>
       <c r="B45" s="80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C45" s="62">
         <v>73</v>
       </c>
       <c r="D45" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" s="61" t="s">
         <v>201</v>
-      </c>
-      <c r="E45" s="61" t="s">
-        <v>202</v>
       </c>
       <c r="F45" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6122,16 +6165,16 @@
         <v>3</v>
       </c>
       <c r="B46" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="62">
         <v>74</v>
       </c>
       <c r="D46" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="78" t="s">
         <v>204</v>
-      </c>
-      <c r="E46" s="78" t="s">
-        <v>205</v>
       </c>
       <c r="F46" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6189,16 +6232,16 @@
         <v>3</v>
       </c>
       <c r="B47" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C47" s="62">
         <v>75</v>
       </c>
       <c r="D47" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="E47" s="78" t="s">
         <v>207</v>
-      </c>
-      <c r="E47" s="78" t="s">
-        <v>208</v>
       </c>
       <c r="F47" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6257,16 +6300,16 @@
         <v>4</v>
       </c>
       <c r="B48" s="80" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" s="62">
         <v>76</v>
       </c>
       <c r="D48" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="135" t="s">
         <v>210</v>
-      </c>
-      <c r="E48" s="135" t="s">
-        <v>211</v>
       </c>
       <c r="F48" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6324,7 +6367,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C49" s="62">
         <v>77</v>
@@ -6333,7 +6376,7 @@
         <v>196</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F49" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6391,7 +6434,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="80" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C50" s="62">
         <v>78</v>
@@ -6400,7 +6443,7 @@
         <v>196</v>
       </c>
       <c r="E50" s="61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F50" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6455,13 +6498,13 @@
         <v>5</v>
       </c>
       <c r="B51" s="80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C51" s="62">
         <v>79</v>
       </c>
       <c r="D51" s="61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E51" s="78"/>
       <c r="F51" s="79">
@@ -6520,16 +6563,16 @@
         <v>5</v>
       </c>
       <c r="B52" s="80" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C52" s="62">
         <v>80</v>
       </c>
       <c r="D52" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" s="61" t="s">
         <v>219</v>
-      </c>
-      <c r="E52" s="61" t="s">
-        <v>220</v>
       </c>
       <c r="F52" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6587,16 +6630,16 @@
         <v>5</v>
       </c>
       <c r="B53" s="80" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53" s="62">
         <v>81</v>
       </c>
       <c r="D53" s="61" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" s="61" t="s">
         <v>222</v>
-      </c>
-      <c r="E53" s="61" t="s">
-        <v>223</v>
       </c>
       <c r="F53" s="79">
         <v>2.0199999999999999E-2</v>
@@ -6654,13 +6697,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="80" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C54" s="62">
         <v>82</v>
       </c>
       <c r="D54" s="61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E54" s="61"/>
       <c r="F54" s="79">
@@ -6719,16 +6762,16 @@
         <v>6</v>
       </c>
       <c r="B55" s="80" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C55" s="62">
         <v>83</v>
       </c>
       <c r="D55" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="E55" s="61" t="s">
         <v>227</v>
-      </c>
-      <c r="E55" s="61" t="s">
-        <v>228</v>
       </c>
       <c r="F55" s="79">
         <v>1.3899999999999999E-2</v>
@@ -6783,13 +6826,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="80" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C56" s="62">
         <v>84</v>
       </c>
       <c r="D56" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E56" s="78"/>
       <c r="F56" s="79">
@@ -6920,7 +6963,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C59" s="62">
         <v>17</v>
@@ -6929,7 +6972,7 @@
         <v>196</v>
       </c>
       <c r="E59" s="148" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F59" s="79">
         <v>3.2000000000000002E-3</v>
@@ -6987,13 +7030,13 @@
         <v>8</v>
       </c>
       <c r="B60" s="80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C60" s="62">
         <v>18</v>
       </c>
       <c r="D60" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E60" s="78"/>
       <c r="F60" s="79">
@@ -7049,13 +7092,13 @@
         <v>8</v>
       </c>
       <c r="B61" s="80" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C61" s="62">
         <v>19</v>
       </c>
       <c r="D61" s="61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E61" s="78"/>
       <c r="F61" s="79">
@@ -7111,13 +7154,13 @@
         <v>8</v>
       </c>
       <c r="B62" s="80" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C62" s="62">
         <v>20</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E62" s="78"/>
       <c r="F62" s="79">
@@ -7173,13 +7216,13 @@
         <v>9</v>
       </c>
       <c r="B63" s="80" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C63" s="62">
         <v>21</v>
       </c>
       <c r="D63" s="148" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E63" s="181" t="s">
         <v>110</v>
@@ -7240,7 +7283,7 @@
         <v>9</v>
       </c>
       <c r="B64" s="80" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C64" s="62">
         <v>22</v>
@@ -7302,7 +7345,7 @@
         <v>9</v>
       </c>
       <c r="B65" s="80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C65" s="62">
         <v>23</v>
@@ -7320,7 +7363,7 @@
         <v>1528.23</v>
       </c>
       <c r="H65" s="124">
-        <f>G65</f>
+        <f t="shared" ref="H65" si="26">G65</f>
         <v>1528.23</v>
       </c>
       <c r="I65" s="73">
@@ -7369,13 +7412,13 @@
         <v>10</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C66" s="62">
         <v>24</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E66" s="78"/>
       <c r="F66" s="79">
@@ -7434,16 +7477,16 @@
         <v>10</v>
       </c>
       <c r="B67" s="80" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C67" s="62">
         <v>25</v>
       </c>
       <c r="D67" s="61" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" s="61" t="s">
         <v>244</v>
-      </c>
-      <c r="E67" s="61" t="s">
-        <v>245</v>
       </c>
       <c r="F67" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7451,7 +7494,7 @@
       <c r="G67" s="72">
         <v>1528.25</v>
       </c>
-      <c r="H67" s="124">
+      <c r="H67" s="231">
         <v>1328.25</v>
       </c>
       <c r="I67" s="73">
@@ -7500,7 +7543,7 @@
         <v>10</v>
       </c>
       <c r="B68" s="80" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C68" s="62">
         <v>26</v>
@@ -7564,13 +7607,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C69" s="62">
         <v>27</v>
       </c>
       <c r="D69" s="61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E69" s="78"/>
       <c r="F69" s="79">
@@ -7593,7 +7636,7 @@
         <v>60.998612000000001</v>
       </c>
       <c r="L69" s="74">
-        <f t="shared" ref="L69:L90" si="26">M$1*F69</f>
+        <f t="shared" ref="L69:L90" si="27">M$1*F69</f>
         <v>720</v>
       </c>
       <c r="M69" s="133">
@@ -7605,11 +7648,11 @@
         <v>112.29256000000001</v>
       </c>
       <c r="O69" s="133">
-        <f t="shared" ref="O69:O90" si="27">I$2*F69</f>
+        <f t="shared" ref="O69:O90" si="28">I$2*F69</f>
         <v>240</v>
       </c>
       <c r="P69" s="75">
-        <f t="shared" ref="P69:P90" si="28">ROUND(SUM(I69:O69),0) + R69</f>
+        <f t="shared" ref="P69:P90" si="29">ROUND(SUM(I69:O69),0) + R69</f>
         <v>11748.27</v>
       </c>
       <c r="Q69" s="76">
@@ -7617,7 +7660,7 @@
         <v>12100.27</v>
       </c>
       <c r="R69" s="45">
-        <f t="shared" ref="R69:R90" si="29">ROUND(0.001+C69/100,2)</f>
+        <f t="shared" ref="R69:R90" si="30">ROUND(0.001+C69/100,2)</f>
         <v>0.27</v>
       </c>
     </row>
@@ -7626,13 +7669,13 @@
         <v>11</v>
       </c>
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="62">
         <v>28</v>
       </c>
       <c r="D70" s="61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E70" s="78"/>
       <c r="F70" s="79">
@@ -7655,7 +7698,7 @@
         <v>60.998612000000001</v>
       </c>
       <c r="L70" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>720</v>
       </c>
       <c r="M70" s="133">
@@ -7667,11 +7710,11 @@
         <v>112.29256000000001</v>
       </c>
       <c r="O70" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>240</v>
       </c>
       <c r="P70" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>11748.28</v>
       </c>
       <c r="Q70" s="76">
@@ -7679,7 +7722,7 @@
         <v>12100.28</v>
       </c>
       <c r="R70" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
@@ -7688,7 +7731,7 @@
         <v>11</v>
       </c>
       <c r="B71" s="80" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C71" s="62">
         <v>29</v>
@@ -7697,7 +7740,7 @@
         <v>122</v>
       </c>
       <c r="E71" s="61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F71" s="79">
         <v>2.0000000000000001E-4</v>
@@ -7721,7 +7764,7 @@
         <v>60.998612000000001</v>
       </c>
       <c r="L71" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>720</v>
       </c>
       <c r="M71" s="133">
@@ -7733,11 +7776,11 @@
         <v>112.29256000000001</v>
       </c>
       <c r="O71" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>240</v>
       </c>
       <c r="P71" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1298.29</v>
       </c>
       <c r="Q71" s="76">
@@ -7745,14 +7788,14 @@
         <v>1337.29</v>
       </c>
       <c r="R71" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="62"/>
       <c r="B72" s="81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C72" s="62">
         <v>30</v>
@@ -7761,7 +7804,7 @@
         <v>122</v>
       </c>
       <c r="E72" s="148" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F72" s="83">
         <v>2.0000000000000001E-4</v>
@@ -7786,7 +7829,7 @@
         <v>60.998612000000001</v>
       </c>
       <c r="L72" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>720</v>
       </c>
       <c r="M72" s="133">
@@ -7798,11 +7841,11 @@
         <v>112.29256000000001</v>
       </c>
       <c r="O72" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>240</v>
       </c>
       <c r="P72" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1381.3</v>
       </c>
       <c r="Q72" s="76">
@@ -7810,14 +7853,14 @@
         <v>1422.3</v>
       </c>
       <c r="R72" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.3</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="62"/>
       <c r="B73" s="81" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C73" s="62">
         <v>31</v>
@@ -7846,7 +7889,7 @@
         <v>60.998612000000001</v>
       </c>
       <c r="L73" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>720</v>
       </c>
       <c r="M73" s="133">
@@ -7858,11 +7901,11 @@
         <v>112.29256000000001</v>
       </c>
       <c r="O73" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>240</v>
       </c>
       <c r="P73" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5493.31</v>
       </c>
       <c r="Q73" s="76">
@@ -7870,20 +7913,20 @@
         <v>5658.31</v>
       </c>
       <c r="R73" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.31</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="62"/>
       <c r="B74" s="81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C74" s="62">
         <v>32</v>
       </c>
       <c r="D74" s="82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E74" s="82"/>
       <c r="F74" s="83">
@@ -7906,7 +7949,7 @@
         <v>4818.8903480000008</v>
       </c>
       <c r="L74" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>56880.000000000007</v>
       </c>
       <c r="M74" s="133">
@@ -7918,11 +7961,11 @@
         <v>8871.1122400000022</v>
       </c>
       <c r="O74" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>18960.000000000004</v>
       </c>
       <c r="P74" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2418690.3199999998</v>
       </c>
       <c r="Q74" s="76">
@@ -7930,14 +7973,14 @@
         <v>2491251.3199999998</v>
       </c>
       <c r="R74" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.32</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="62"/>
       <c r="B75" s="81" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C75" s="62">
         <v>1</v>
@@ -7966,7 +8009,7 @@
         <v>1860.457666</v>
       </c>
       <c r="L75" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>21960</v>
       </c>
       <c r="M75" s="133">
@@ -7978,11 +8021,11 @@
         <v>3424.9230800000005</v>
       </c>
       <c r="O75" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7320.0000000000009</v>
       </c>
       <c r="P75" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>282201.01</v>
       </c>
       <c r="Q75" s="76">
@@ -7990,20 +8033,20 @@
         <v>290667.01</v>
       </c>
       <c r="R75" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.01</v>
       </c>
     </row>
     <row r="76" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="62"/>
       <c r="B76" s="81" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C76" s="62">
         <v>2</v>
       </c>
       <c r="D76" s="182" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E76" s="182"/>
       <c r="F76" s="83">
@@ -8029,7 +8072,7 @@
         <v>1951.955584</v>
       </c>
       <c r="L76" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23040</v>
       </c>
       <c r="M76" s="133">
@@ -8041,11 +8084,11 @@
         <v>3593.3619200000003</v>
       </c>
       <c r="O76" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7680</v>
       </c>
       <c r="P76" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>44208.02</v>
       </c>
       <c r="Q76" s="76">
@@ -8053,20 +8096,20 @@
         <v>45534.02</v>
       </c>
       <c r="R76" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.02</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="62"/>
       <c r="B77" s="81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C77" s="62">
         <v>3</v>
       </c>
       <c r="D77" s="182" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E77" s="182"/>
       <c r="F77" s="83">
@@ -8092,7 +8135,7 @@
         <v>1738.4604420000001</v>
       </c>
       <c r="L77" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20520</v>
       </c>
       <c r="M77" s="133">
@@ -8104,11 +8147,11 @@
         <v>3200.3379600000003</v>
       </c>
       <c r="O77" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6840</v>
       </c>
       <c r="P77" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>39373.03</v>
       </c>
       <c r="Q77" s="76">
@@ -8116,14 +8159,14 @@
         <v>40554.03</v>
       </c>
       <c r="R77" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="62"/>
       <c r="B78" s="81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C78" s="62">
         <v>4</v>
@@ -8155,7 +8198,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L78" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M78" s="133">
@@ -8167,11 +8210,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O78" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P78" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36610.04</v>
       </c>
       <c r="Q78" s="76">
@@ -8179,14 +8222,14 @@
         <v>37708.04</v>
       </c>
       <c r="R78" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.04</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="62"/>
       <c r="B79" s="81" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C79" s="62">
         <v>5</v>
@@ -8217,7 +8260,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L79" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M79" s="133">
@@ -8229,11 +8272,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O79" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P79" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>78306.05</v>
       </c>
       <c r="Q79" s="76">
@@ -8241,20 +8284,20 @@
         <v>80655.05</v>
       </c>
       <c r="R79" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="62"/>
       <c r="B80" s="81" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C80" s="62">
         <v>6</v>
       </c>
       <c r="D80" s="82" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E80" s="78" t="s">
         <v>110</v>
@@ -8265,11 +8308,11 @@
       <c r="G80" s="72">
         <v>105752.06</v>
       </c>
-      <c r="H80" s="186">
+      <c r="H80" s="235">
         <f>100452.06</f>
         <v>100452.06</v>
       </c>
-      <c r="I80" s="187">
+      <c r="I80" s="236">
         <f t="shared" si="20"/>
         <v>5300</v>
       </c>
@@ -8282,7 +8325,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L80" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M80" s="133">
@@ -8294,11 +8337,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O80" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P80" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>42069.06</v>
       </c>
       <c r="Q80" s="76">
@@ -8306,11 +8349,11 @@
         <v>43331.06</v>
       </c>
       <c r="R80" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.06</v>
       </c>
-      <c r="S80" s="188" t="s">
-        <v>265</v>
+      <c r="S80" s="186" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8318,7 +8361,7 @@
         <v>12</v>
       </c>
       <c r="B81" s="81" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C81" s="62">
         <v>7</v>
@@ -8349,7 +8392,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L81" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M81" s="133">
@@ -8361,11 +8404,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O81" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P81" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>145534.07</v>
       </c>
       <c r="Q81" s="76">
@@ -8373,7 +8416,7 @@
         <v>149900.07</v>
       </c>
       <c r="R81" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -8382,7 +8425,7 @@
         <v>12</v>
       </c>
       <c r="B82" s="80" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C82" s="62">
         <v>8</v>
@@ -8411,7 +8454,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L82" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M82" s="133">
@@ -8423,11 +8466,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O82" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P82" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>145534.07999999999</v>
       </c>
       <c r="Q82" s="76">
@@ -8435,7 +8478,7 @@
         <v>149900.07999999999</v>
       </c>
       <c r="R82" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.08</v>
       </c>
     </row>
@@ -8444,7 +8487,7 @@
         <v>12</v>
       </c>
       <c r="B83" s="80" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C83" s="62">
         <v>9</v>
@@ -8454,7 +8497,7 @@
       </c>
       <c r="E83" s="147" t="str">
         <f>E44</f>
-        <v>Agustina Malfigliaccio y Alan Pons</v>
+        <v>Luz Maria Alberio</v>
       </c>
       <c r="F83" s="83">
         <v>5.3E-3</v>
@@ -8476,7 +8519,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L83" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M83" s="133">
@@ -8488,11 +8531,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O83" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P83" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>78306.09</v>
       </c>
       <c r="Q83" s="76">
@@ -8500,14 +8543,14 @@
         <v>80655.09</v>
       </c>
       <c r="R83" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="62"/>
       <c r="B84" s="80" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C84" s="80">
         <v>10</v>
@@ -8536,7 +8579,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L84" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M84" s="133">
@@ -8548,11 +8591,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O84" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P84" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>241834.1</v>
       </c>
       <c r="Q84" s="76">
@@ -8560,14 +8603,14 @@
         <v>249089.1</v>
       </c>
       <c r="R84" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="62"/>
       <c r="B85" s="80" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C85" s="80">
         <v>11</v>
@@ -8576,7 +8619,7 @@
         <v>196</v>
       </c>
       <c r="E85" s="63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F85" s="71">
         <v>5.3E-3</v>
@@ -8601,7 +8644,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L85" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M85" s="133">
@@ -8613,11 +8656,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O85" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P85" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>105537.11</v>
       </c>
       <c r="Q85" s="76">
@@ -8625,14 +8668,14 @@
         <v>108703.11</v>
       </c>
       <c r="R85" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.11</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="62"/>
       <c r="B86" s="80" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C86" s="80">
         <v>12</v>
@@ -8666,7 +8709,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L86" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M86" s="133">
@@ -8678,11 +8721,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O86" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P86" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36610.120000000003</v>
       </c>
       <c r="Q86" s="76">
@@ -8690,14 +8733,14 @@
         <v>37708.120000000003</v>
       </c>
       <c r="R86" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.12</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="62"/>
       <c r="B87" s="62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C87" s="62">
         <v>13</v>
@@ -8729,7 +8772,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L87" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M87" s="133">
@@ -8741,11 +8784,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O87" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P87" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36610.129999999997</v>
       </c>
       <c r="Q87" s="76">
@@ -8753,14 +8796,14 @@
         <v>37708.129999999997</v>
       </c>
       <c r="R87" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.13</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="62"/>
       <c r="B88" s="62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C88" s="62">
         <v>14</v>
@@ -8769,7 +8812,7 @@
         <v>156</v>
       </c>
       <c r="E88" s="63" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="71">
         <v>5.3E-3</v>
@@ -8791,7 +8834,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L88" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M88" s="133">
@@ -8803,11 +8846,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O88" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P88" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>75727.14</v>
       </c>
       <c r="Q88" s="76">
@@ -8815,14 +8858,14 @@
         <v>77999.14</v>
       </c>
       <c r="R88" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="62"/>
       <c r="B89" s="62" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C89" s="62">
         <v>15</v>
@@ -8857,7 +8900,7 @@
         <v>1616.4632180000001</v>
       </c>
       <c r="L89" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19080</v>
       </c>
       <c r="M89" s="133">
@@ -8869,11 +8912,11 @@
         <v>2975.7528400000001</v>
       </c>
       <c r="O89" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6360</v>
       </c>
       <c r="P89" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36610.15</v>
       </c>
       <c r="Q89" s="76">
@@ -8881,14 +8924,14 @@
         <v>37708.15</v>
       </c>
       <c r="R89" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="61"/>
       <c r="B90" s="61" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C90" s="62">
         <v>16</v>
@@ -8905,7 +8948,7 @@
       <c r="G90" s="161">
         <v>88696.16</v>
       </c>
-      <c r="H90" s="189">
+      <c r="H90" s="187">
         <f>G90</f>
         <v>88696.16</v>
       </c>
@@ -8922,7 +8965,7 @@
         <v>1890.956972</v>
       </c>
       <c r="L90" s="74">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>22320</v>
       </c>
       <c r="M90" s="133">
@@ -8934,11 +8977,11 @@
         <v>3481.06936</v>
       </c>
       <c r="O90" s="133">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7440</v>
       </c>
       <c r="P90" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>42826.16</v>
       </c>
       <c r="Q90" s="76">
@@ -8946,7 +8989,7 @@
         <v>44111.16</v>
       </c>
       <c r="R90" s="45">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.16</v>
       </c>
     </row>
@@ -8977,31 +9020,31 @@
       <c r="D92" s="173"/>
       <c r="E92" s="173"/>
       <c r="F92" s="174">
-        <f t="shared" ref="F92:L92" si="30">SUM(F5:F91)</f>
+        <f t="shared" ref="F92:L92" si="31">SUM(F5:F91)</f>
         <v>0.99999999999999956</v>
       </c>
       <c r="G92" s="175">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>11779913.699999999</v>
       </c>
       <c r="H92" s="176">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6723784.4099999983</v>
       </c>
       <c r="I92" s="177">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5056129.2899999991</v>
       </c>
       <c r="J92" s="178">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>155048.49359999999</v>
       </c>
       <c r="K92" s="178">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>304993.06000000075</v>
       </c>
       <c r="L92" s="179">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3600000</v>
       </c>
       <c r="M92" s="179">
@@ -9033,100 +9076,107 @@
       <c r="H94" s="125"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="192" t="str">
+      <c r="D95" s="201" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</v>
       </c>
-      <c r="E95" s="193"/>
-      <c r="F95" s="193"/>
-      <c r="G95" s="193"/>
-      <c r="H95" s="193"/>
-      <c r="I95" s="193"/>
-      <c r="J95" s="193"/>
-      <c r="K95" s="193"/>
-      <c r="L95" s="193"/>
-      <c r="M95" s="193"/>
-      <c r="N95" s="193"/>
-      <c r="O95" s="193"/>
-      <c r="P95" s="193"/>
+      <c r="E95" s="197"/>
+      <c r="F95" s="197"/>
+      <c r="G95" s="197"/>
+      <c r="H95" s="197"/>
+      <c r="I95" s="197"/>
+      <c r="J95" s="197"/>
+      <c r="K95" s="197"/>
+      <c r="L95" s="197"/>
+      <c r="M95" s="197"/>
+      <c r="N95" s="197"/>
+      <c r="O95" s="197"/>
+      <c r="P95" s="197"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="193"/>
-      <c r="E96" s="193"/>
-      <c r="F96" s="193"/>
-      <c r="G96" s="193"/>
-      <c r="H96" s="193"/>
-      <c r="I96" s="193"/>
-      <c r="J96" s="193"/>
-      <c r="K96" s="193"/>
-      <c r="L96" s="193"/>
-      <c r="M96" s="193"/>
-      <c r="N96" s="193"/>
-      <c r="O96" s="193"/>
-      <c r="P96" s="193"/>
+      <c r="D96" s="197"/>
+      <c r="E96" s="197"/>
+      <c r="F96" s="197"/>
+      <c r="G96" s="197"/>
+      <c r="H96" s="197"/>
+      <c r="I96" s="197"/>
+      <c r="J96" s="197"/>
+      <c r="K96" s="197"/>
+      <c r="L96" s="197"/>
+      <c r="M96" s="197"/>
+      <c r="N96" s="197"/>
+      <c r="O96" s="197"/>
+      <c r="P96" s="197"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="193"/>
-      <c r="E97" s="193"/>
-      <c r="F97" s="193"/>
-      <c r="G97" s="193"/>
-      <c r="H97" s="193"/>
-      <c r="I97" s="193"/>
-      <c r="J97" s="193"/>
-      <c r="K97" s="193"/>
-      <c r="L97" s="193"/>
-      <c r="M97" s="193"/>
-      <c r="N97" s="193"/>
-      <c r="O97" s="193"/>
-      <c r="P97" s="193"/>
+      <c r="D97" s="197"/>
+      <c r="E97" s="197"/>
+      <c r="F97" s="197"/>
+      <c r="G97" s="197"/>
+      <c r="H97" s="197"/>
+      <c r="I97" s="197"/>
+      <c r="J97" s="197"/>
+      <c r="K97" s="197"/>
+      <c r="L97" s="197"/>
+      <c r="M97" s="197"/>
+      <c r="N97" s="197"/>
+      <c r="O97" s="197"/>
+      <c r="P97" s="197"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="193"/>
-      <c r="E98" s="193"/>
-      <c r="F98" s="193"/>
-      <c r="G98" s="193"/>
-      <c r="H98" s="193"/>
-      <c r="I98" s="193"/>
-      <c r="J98" s="193"/>
-      <c r="K98" s="193"/>
-      <c r="L98" s="193"/>
-      <c r="M98" s="193"/>
-      <c r="N98" s="193"/>
-      <c r="O98" s="193"/>
-      <c r="P98" s="193"/>
+      <c r="D98" s="197"/>
+      <c r="E98" s="197"/>
+      <c r="F98" s="197"/>
+      <c r="G98" s="197"/>
+      <c r="H98" s="197"/>
+      <c r="I98" s="197"/>
+      <c r="J98" s="197"/>
+      <c r="K98" s="197"/>
+      <c r="L98" s="197"/>
+      <c r="M98" s="197"/>
+      <c r="N98" s="197"/>
+      <c r="O98" s="197"/>
+      <c r="P98" s="197"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="193"/>
-      <c r="E99" s="193"/>
-      <c r="F99" s="193"/>
-      <c r="G99" s="193"/>
-      <c r="H99" s="193"/>
-      <c r="I99" s="193"/>
-      <c r="J99" s="193"/>
-      <c r="K99" s="193"/>
-      <c r="L99" s="193"/>
-      <c r="M99" s="193"/>
-      <c r="N99" s="193"/>
-      <c r="O99" s="193"/>
-      <c r="P99" s="193"/>
+      <c r="D99" s="197"/>
+      <c r="E99" s="197"/>
+      <c r="F99" s="197"/>
+      <c r="G99" s="197"/>
+      <c r="H99" s="197"/>
+      <c r="I99" s="197"/>
+      <c r="J99" s="197"/>
+      <c r="K99" s="197"/>
+      <c r="L99" s="197"/>
+      <c r="M99" s="197"/>
+      <c r="N99" s="197"/>
+      <c r="O99" s="197"/>
+      <c r="P99" s="197"/>
     </row>
     <row r="100" spans="4:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="193"/>
-      <c r="E100" s="193"/>
-      <c r="F100" s="193"/>
-      <c r="G100" s="193"/>
-      <c r="H100" s="193"/>
-      <c r="I100" s="193"/>
-      <c r="J100" s="193"/>
-      <c r="K100" s="193"/>
-      <c r="L100" s="193"/>
-      <c r="M100" s="193"/>
-      <c r="N100" s="193"/>
-      <c r="O100" s="193"/>
-      <c r="P100" s="193"/>
+      <c r="D100" s="197"/>
+      <c r="E100" s="197"/>
+      <c r="F100" s="197"/>
+      <c r="G100" s="197"/>
+      <c r="H100" s="197"/>
+      <c r="I100" s="197"/>
+      <c r="J100" s="197"/>
+      <c r="K100" s="197"/>
+      <c r="L100" s="197"/>
+      <c r="M100" s="197"/>
+      <c r="N100" s="197"/>
+      <c r="O100" s="197"/>
+      <c r="P100" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D95:P100"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
@@ -9143,13 +9193,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D95:P100"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape"/>
@@ -9157,19 +9200,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="D4:D8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8AEA40-856C-4C69-BDF8-B1FFAA30BA95}">
+  <dimension ref="D4:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="4" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D4" s="190" t="s">
-        <v>278</v>
+      <c r="D4" s="188" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D8" s="49" t="s">
-        <v>279</v>
-      </c>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="234" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D15" s="233" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D18" s="232" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D21" s="237" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="237"/>
+      <c r="F21" s="237"/>
+      <c r="G21" s="237"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VERGARA/Junio/vergara JUNIO.xlsx
+++ b/VERGARA/Junio/vergara JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E638F5-784A-4491-82F4-318B7535D8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A303A998-BF9F-443C-9087-2B08AC17BEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -816,9 +816,6 @@
     <t>Luz Maria Alberio</t>
   </si>
   <si>
-    <t>hay que agregar a luzalberio@gmail.com  a la cadena, es nueva inquilina del 10D</t>
-  </si>
-  <si>
     <t>Honorarios administracion - Mes de MAYO Y JUNIO</t>
   </si>
   <si>
@@ -880,6 +877,9 @@
   </si>
   <si>
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</t>
+  </si>
+  <si>
+    <t>santiago flores debe quedar sin deuda, no le imputamos el pago correctamente en mayo, y los punitorios a restar (mal cobrados son de $21080)</t>
   </si>
 </sst>
 </file>
@@ -1516,7 +1516,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1788,6 +1788,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2287,12 +2288,12 @@
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="199" t="s">
+      <c r="B5" s="200" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="199"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -2306,49 +2307,49 @@
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="188"/>
+      <c r="C8" s="189"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="188"/>
-      <c r="C9" s="188"/>
+      <c r="B9" s="189"/>
+      <c r="C9" s="189"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
+      <c r="B10" s="189"/>
+      <c r="C10" s="189"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
-        <v>283</v>
-      </c>
-      <c r="B13" s="202"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
+      <c r="A13" s="202" t="s">
+        <v>282</v>
+      </c>
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
-      <c r="B14" s="202"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
+      <c r="A14" s="203"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="202"/>
-      <c r="B15" s="202"/>
-      <c r="C15" s="202"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
+      <c r="A15" s="203"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
     </row>
     <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
-      <c r="B16" s="202"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2383,7 +2384,7 @@
         <v>1033560</v>
       </c>
       <c r="E22" s="86" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2446,10 +2447,10 @@
       <c r="E27" s="89"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="189" t="s">
+      <c r="A28" s="190" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="190"/>
+      <c r="B28" s="191"/>
       <c r="C28" s="5"/>
       <c r="D28" s="182">
         <v>35000</v>
@@ -2459,17 +2460,17 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="189" t="s">
-        <v>263</v>
-      </c>
-      <c r="B29" s="190"/>
+      <c r="A29" s="190" t="s">
+        <v>262</v>
+      </c>
+      <c r="B29" s="191"/>
       <c r="C29" s="5"/>
       <c r="D29" s="182">
         <f>470000*2</f>
         <v>940000</v>
       </c>
       <c r="E29" s="90" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2506,10 +2507,10 @@
       <c r="G32" s="153"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="189" t="s">
+      <c r="A33" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="190"/>
+      <c r="B33" s="191"/>
       <c r="C33" s="53"/>
       <c r="D33" s="181">
         <v>719.9</v>
@@ -2547,7 +2548,7 @@
         <v>297953.51</v>
       </c>
       <c r="E36" s="115" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G36" s="120"/>
     </row>
@@ -2563,7 +2564,7 @@
         <v>26936.54</v>
       </c>
       <c r="E37" s="101" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2632,7 +2633,7 @@
         <v>169258.92</v>
       </c>
       <c r="E42" s="99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2645,20 +2646,20 @@
         <v>50000</v>
       </c>
       <c r="E43" s="99" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="189" t="s">
+      <c r="A44" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="190"/>
+      <c r="B44" s="191"/>
       <c r="C44" s="5"/>
       <c r="D44" s="181">
         <v>84984.35</v>
       </c>
       <c r="E44" s="99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2684,7 +2685,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="149" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B47" s="150"/>
       <c r="C47" s="63"/>
@@ -2692,27 +2693,27 @@
         <v>38950</v>
       </c>
       <c r="E47" s="151" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="190" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="189" t="s">
-        <v>273</v>
-      </c>
-      <c r="B48" s="190"/>
+      <c r="B48" s="191"/>
       <c r="C48" s="54"/>
       <c r="D48" s="181">
         <v>110000</v>
       </c>
       <c r="E48" s="151" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="194" t="s">
+      <c r="A49" s="195" t="s">
         <v>257</v>
       </c>
-      <c r="B49" s="195"/>
+      <c r="B49" s="196"/>
       <c r="C49" s="54"/>
       <c r="D49" s="181">
         <v>110000</v>
@@ -2722,10 +2723,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="189" t="s">
+      <c r="A50" s="190" t="s">
         <v>260</v>
       </c>
-      <c r="B50" s="190"/>
+      <c r="B50" s="191"/>
       <c r="C50" s="54"/>
       <c r="D50" s="181">
         <v>135000</v>
@@ -2736,7 +2737,7 @@
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="137" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B51" s="126"/>
       <c r="C51" s="54"/>
@@ -2744,27 +2745,27 @@
         <v>25000</v>
       </c>
       <c r="E51" s="151" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="189" t="s">
-        <v>275</v>
-      </c>
-      <c r="B52" s="190"/>
+      <c r="A52" s="190" t="s">
+        <v>274</v>
+      </c>
+      <c r="B52" s="191"/>
       <c r="C52" s="54"/>
       <c r="D52" s="181">
         <v>150000</v>
       </c>
       <c r="E52" s="152" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="191" t="s">
-        <v>271</v>
-      </c>
-      <c r="B53" s="192"/>
+      <c r="A53" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="B53" s="193"/>
       <c r="C53" s="5"/>
       <c r="D53" s="181">
         <v>110000</v>
@@ -2774,10 +2775,10 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="189" t="s">
+      <c r="A54" s="190" t="s">
         <v>259</v>
       </c>
-      <c r="B54" s="190"/>
+      <c r="B54" s="191"/>
       <c r="C54" s="5"/>
       <c r="D54" s="97">
         <v>51150</v>
@@ -2785,8 +2786,8 @@
       <c r="E54" s="151" t="s">
         <v>256</v>
       </c>
-      <c r="I54" s="189"/>
-      <c r="J54" s="190"/>
+      <c r="I54" s="190"/>
+      <c r="J54" s="191"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
@@ -2897,17 +2898,17 @@
       <c r="E66" s="111"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="189" t="s">
-        <v>280</v>
-      </c>
-      <c r="B67" s="190"/>
+      <c r="A67" s="190" t="s">
+        <v>279</v>
+      </c>
+      <c r="B67" s="191"/>
       <c r="C67" s="5"/>
       <c r="D67" s="97">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
       <c r="E67" s="94" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2930,12 +2931,12 @@
     <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="196" t="s">
+      <c r="A72" s="197" t="s">
         <v>43</v>
       </c>
-      <c r="B72" s="197"/>
-      <c r="C72" s="197"/>
-      <c r="D72" s="198"/>
+      <c r="B72" s="198"/>
+      <c r="C72" s="198"/>
+      <c r="D72" s="199"/>
       <c r="E72" s="144"/>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3101,16 +3102,16 @@
       <c r="F92" s="123"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="193" t="s">
+      <c r="A93" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="B93" s="188"/>
-      <c r="C93" s="188"/>
+      <c r="B93" s="189"/>
+      <c r="C93" s="189"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="188"/>
-      <c r="B94" s="188"/>
-      <c r="C94" s="188"/>
+      <c r="A94" s="189"/>
+      <c r="B94" s="189"/>
+      <c r="C94" s="189"/>
     </row>
     <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="53"/>
@@ -3145,32 +3146,32 @@
       <c r="M99" s="7"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="187"/>
-      <c r="B100" s="188"/>
-      <c r="C100" s="188"/>
-      <c r="D100" s="188"/>
-      <c r="E100" s="188"/>
+      <c r="A100" s="188"/>
+      <c r="B100" s="189"/>
+      <c r="C100" s="189"/>
+      <c r="D100" s="189"/>
+      <c r="E100" s="189"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="188"/>
-      <c r="B101" s="188"/>
-      <c r="C101" s="188"/>
-      <c r="D101" s="188"/>
-      <c r="E101" s="188"/>
+      <c r="A101" s="189"/>
+      <c r="B101" s="189"/>
+      <c r="C101" s="189"/>
+      <c r="D101" s="189"/>
+      <c r="E101" s="189"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="188"/>
-      <c r="B102" s="188"/>
-      <c r="C102" s="188"/>
-      <c r="D102" s="188"/>
-      <c r="E102" s="188"/>
+      <c r="A102" s="189"/>
+      <c r="B102" s="189"/>
+      <c r="C102" s="189"/>
+      <c r="D102" s="189"/>
+      <c r="E102" s="189"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="188"/>
-      <c r="B103" s="188"/>
-      <c r="C103" s="188"/>
-      <c r="D103" s="188"/>
-      <c r="E103" s="188"/>
+      <c r="A103" s="189"/>
+      <c r="B103" s="189"/>
+      <c r="C103" s="189"/>
+      <c r="D103" s="189"/>
+      <c r="E103" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3230,10 +3231,10 @@
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="215">
+      <c r="F1" s="216">
         <v>1241030.1599999999</v>
       </c>
-      <c r="G1" s="213"/>
+      <c r="G1" s="214"/>
       <c r="H1" s="185"/>
       <c r="I1" s="185"/>
       <c r="J1" s="185"/>
@@ -3241,16 +3242,16 @@
         <v>60</v>
       </c>
       <c r="L1" s="185"/>
-      <c r="M1" s="212">
+      <c r="M1" s="213">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="213"/>
+      <c r="N1" s="214"/>
       <c r="O1" s="138"/>
-      <c r="P1" s="211">
+      <c r="P1" s="212">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="188"/>
+      <c r="Q1" s="189"/>
       <c r="R1" s="19"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3261,104 +3262,104 @@
       <c r="E2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="203">
+      <c r="F2" s="204">
         <v>561462.80000000005</v>
       </c>
-      <c r="G2" s="204"/>
+      <c r="G2" s="205"/>
       <c r="H2" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="214">
+      <c r="I2" s="215">
         <v>1200000</v>
       </c>
-      <c r="J2" s="204"/>
+      <c r="J2" s="205"/>
       <c r="K2" s="185" t="s">
         <v>63</v>
       </c>
       <c r="L2" s="185"/>
-      <c r="M2" s="214">
+      <c r="M2" s="215">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="205"/>
       <c r="O2" s="140"/>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="220"/>
+      <c r="P2" s="220"/>
+      <c r="Q2" s="221"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="216" t="s">
+      <c r="A3" s="217" t="s">
         <v>64</v>
       </c>
       <c r="B3" s="117"/>
-      <c r="C3" s="205" t="s">
+      <c r="C3" s="206" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="205" t="s">
+      <c r="D3" s="206" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="210" t="s">
+      <c r="E3" s="211" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="205" t="s">
+      <c r="F3" s="206" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="207" t="s">
+      <c r="G3" s="208" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="205" t="s">
+      <c r="H3" s="206" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="218" t="s">
+      <c r="I3" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="207" t="s">
+      <c r="J3" s="208" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="209" t="str">
+      <c r="K3" s="210" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="207" t="s">
+      <c r="L3" s="208" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="207" t="s">
+      <c r="M3" s="208" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="207" t="s">
+      <c r="N3" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="207" t="s">
+      <c r="O3" s="208" t="s">
         <v>75</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="221" t="s">
+      <c r="Q3" s="222" t="s">
         <v>77</v>
       </c>
       <c r="T3" s="44"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="217"/>
+      <c r="A4" s="218"/>
       <c r="B4" s="118"/>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="206"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="206"/>
-      <c r="L4" s="208"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
+      <c r="C4" s="207"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="209"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="207"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="209"/>
+      <c r="M4" s="209"/>
+      <c r="N4" s="209"/>
+      <c r="O4" s="209"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="Q4" s="206"/>
+      <c r="Q4" s="207"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61"/>
@@ -3699,7 +3700,7 @@
       <c r="D10" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="187" t="s">
         <v>91</v>
       </c>
       <c r="F10" s="69">
@@ -6605,7 +6606,7 @@
         <v>0.81</v>
       </c>
       <c r="T53" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7076,7 +7077,7 @@
         <v>20</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
@@ -9006,97 +9007,97 @@
       <c r="H94" s="120"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="187" t="str">
+      <c r="D95" s="188" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E95" s="188"/>
-      <c r="F95" s="188"/>
-      <c r="G95" s="188"/>
-      <c r="H95" s="188"/>
-      <c r="I95" s="188"/>
-      <c r="J95" s="188"/>
-      <c r="K95" s="188"/>
-      <c r="L95" s="188"/>
-      <c r="M95" s="188"/>
-      <c r="N95" s="188"/>
-      <c r="O95" s="188"/>
-      <c r="P95" s="188"/>
+      <c r="E95" s="189"/>
+      <c r="F95" s="189"/>
+      <c r="G95" s="189"/>
+      <c r="H95" s="189"/>
+      <c r="I95" s="189"/>
+      <c r="J95" s="189"/>
+      <c r="K95" s="189"/>
+      <c r="L95" s="189"/>
+      <c r="M95" s="189"/>
+      <c r="N95" s="189"/>
+      <c r="O95" s="189"/>
+      <c r="P95" s="189"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="188"/>
-      <c r="E96" s="188"/>
-      <c r="F96" s="188"/>
-      <c r="G96" s="188"/>
-      <c r="H96" s="188"/>
-      <c r="I96" s="188"/>
-      <c r="J96" s="188"/>
-      <c r="K96" s="188"/>
-      <c r="L96" s="188"/>
-      <c r="M96" s="188"/>
-      <c r="N96" s="188"/>
-      <c r="O96" s="188"/>
-      <c r="P96" s="188"/>
+      <c r="D96" s="189"/>
+      <c r="E96" s="189"/>
+      <c r="F96" s="189"/>
+      <c r="G96" s="189"/>
+      <c r="H96" s="189"/>
+      <c r="I96" s="189"/>
+      <c r="J96" s="189"/>
+      <c r="K96" s="189"/>
+      <c r="L96" s="189"/>
+      <c r="M96" s="189"/>
+      <c r="N96" s="189"/>
+      <c r="O96" s="189"/>
+      <c r="P96" s="189"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="188"/>
-      <c r="E97" s="188"/>
-      <c r="F97" s="188"/>
-      <c r="G97" s="188"/>
-      <c r="H97" s="188"/>
-      <c r="I97" s="188"/>
-      <c r="J97" s="188"/>
-      <c r="K97" s="188"/>
-      <c r="L97" s="188"/>
-      <c r="M97" s="188"/>
-      <c r="N97" s="188"/>
-      <c r="O97" s="188"/>
-      <c r="P97" s="188"/>
+      <c r="D97" s="189"/>
+      <c r="E97" s="189"/>
+      <c r="F97" s="189"/>
+      <c r="G97" s="189"/>
+      <c r="H97" s="189"/>
+      <c r="I97" s="189"/>
+      <c r="J97" s="189"/>
+      <c r="K97" s="189"/>
+      <c r="L97" s="189"/>
+      <c r="M97" s="189"/>
+      <c r="N97" s="189"/>
+      <c r="O97" s="189"/>
+      <c r="P97" s="189"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="188"/>
-      <c r="E98" s="188"/>
-      <c r="F98" s="188"/>
-      <c r="G98" s="188"/>
-      <c r="H98" s="188"/>
-      <c r="I98" s="188"/>
-      <c r="J98" s="188"/>
-      <c r="K98" s="188"/>
-      <c r="L98" s="188"/>
-      <c r="M98" s="188"/>
-      <c r="N98" s="188"/>
-      <c r="O98" s="188"/>
-      <c r="P98" s="188"/>
+      <c r="D98" s="189"/>
+      <c r="E98" s="189"/>
+      <c r="F98" s="189"/>
+      <c r="G98" s="189"/>
+      <c r="H98" s="189"/>
+      <c r="I98" s="189"/>
+      <c r="J98" s="189"/>
+      <c r="K98" s="189"/>
+      <c r="L98" s="189"/>
+      <c r="M98" s="189"/>
+      <c r="N98" s="189"/>
+      <c r="O98" s="189"/>
+      <c r="P98" s="189"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="188"/>
-      <c r="E99" s="188"/>
-      <c r="F99" s="188"/>
-      <c r="G99" s="188"/>
-      <c r="H99" s="188"/>
-      <c r="I99" s="188"/>
-      <c r="J99" s="188"/>
-      <c r="K99" s="188"/>
-      <c r="L99" s="188"/>
-      <c r="M99" s="188"/>
-      <c r="N99" s="188"/>
-      <c r="O99" s="188"/>
-      <c r="P99" s="188"/>
+      <c r="D99" s="189"/>
+      <c r="E99" s="189"/>
+      <c r="F99" s="189"/>
+      <c r="G99" s="189"/>
+      <c r="H99" s="189"/>
+      <c r="I99" s="189"/>
+      <c r="J99" s="189"/>
+      <c r="K99" s="189"/>
+      <c r="L99" s="189"/>
+      <c r="M99" s="189"/>
+      <c r="N99" s="189"/>
+      <c r="O99" s="189"/>
+      <c r="P99" s="189"/>
     </row>
     <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="188"/>
-      <c r="E100" s="188"/>
-      <c r="F100" s="188"/>
-      <c r="G100" s="188"/>
-      <c r="H100" s="188"/>
-      <c r="I100" s="188"/>
-      <c r="J100" s="188"/>
-      <c r="K100" s="188"/>
-      <c r="L100" s="188"/>
-      <c r="M100" s="188"/>
-      <c r="N100" s="188"/>
-      <c r="O100" s="188"/>
-      <c r="P100" s="188"/>
+      <c r="D100" s="189"/>
+      <c r="E100" s="189"/>
+      <c r="F100" s="189"/>
+      <c r="G100" s="189"/>
+      <c r="H100" s="189"/>
+      <c r="I100" s="189"/>
+      <c r="J100" s="189"/>
+      <c r="K100" s="189"/>
+      <c r="L100" s="189"/>
+      <c r="M100" s="189"/>
+      <c r="N100" s="189"/>
+      <c r="O100" s="189"/>
+      <c r="P100" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -9175,7 +9176,7 @@
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="177" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.25">

--- a/VERGARA/Junio/vergara JUNIO.xlsx
+++ b/VERGARA/Junio/vergara JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\VERGARA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A303A998-BF9F-443C-9087-2B08AC17BEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4841E31-FE4C-486C-B7EE-597EFE05634E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="286">
   <si>
     <t>MAIL: consorciovergara1670@gmail.com</t>
   </si>
@@ -880,6 +880,12 @@
   </si>
   <si>
     <t>santiago flores debe quedar sin deuda, no le imputamos el pago correctamente en mayo, y los punitorios a restar (mal cobrados son de $21080)</t>
+  </si>
+  <si>
+    <t>COCHERA 26 AGREGAR INQUILINO - Matias Zeolla</t>
+  </si>
+  <si>
+    <t>Jose Luis urtibay pago cualquier cosa el tarado, no respeto decimales - Pago extraordinarias de muchas UFS</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1083,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1147,6 +1153,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1516,7 +1528,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1789,14 +1801,28 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1811,38 +1837,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="170" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1853,6 +1847,7 @@
     <xf numFmtId="170" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1860,6 +1855,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1867,9 +1866,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2288,12 +2302,12 @@
       <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="200" t="s">
+      <c r="B5" s="188" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="199"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="190"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
@@ -2307,49 +2321,49 @@
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="201" t="s">
+      <c r="B8" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="189"/>
+      <c r="C8" s="192"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="192"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="189"/>
-      <c r="C10" s="189"/>
+      <c r="B10" s="192"/>
+      <c r="C10" s="192"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="202" t="s">
+      <c r="A13" s="193" t="s">
         <v>282</v>
       </c>
-      <c r="B13" s="203"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="203"/>
-      <c r="B14" s="203"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
+      <c r="A14" s="194"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="203"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
     </row>
     <row r="16" spans="1:5" ht="216" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="203"/>
-      <c r="B16" s="203"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
+      <c r="A16" s="194"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2447,10 +2461,10 @@
       <c r="E27" s="89"/>
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="190" t="s">
+      <c r="A28" s="195" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="191"/>
+      <c r="B28" s="196"/>
       <c r="C28" s="5"/>
       <c r="D28" s="182">
         <v>35000</v>
@@ -2460,10 +2474,10 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="190" t="s">
+      <c r="A29" s="195" t="s">
         <v>262</v>
       </c>
-      <c r="B29" s="191"/>
+      <c r="B29" s="196"/>
       <c r="C29" s="5"/>
       <c r="D29" s="182">
         <f>470000*2</f>
@@ -2507,10 +2521,10 @@
       <c r="G32" s="153"/>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="190" t="s">
+      <c r="A33" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="191"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="53"/>
       <c r="D33" s="181">
         <v>719.9</v>
@@ -2650,10 +2664,10 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="190" t="s">
+      <c r="A44" s="195" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="191"/>
+      <c r="B44" s="196"/>
       <c r="C44" s="5"/>
       <c r="D44" s="181">
         <v>84984.35</v>
@@ -2697,10 +2711,10 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="190" t="s">
+      <c r="A48" s="195" t="s">
         <v>272</v>
       </c>
-      <c r="B48" s="191"/>
+      <c r="B48" s="196"/>
       <c r="C48" s="54"/>
       <c r="D48" s="181">
         <v>110000</v>
@@ -2710,10 +2724,10 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="195" t="s">
+      <c r="A49" s="201" t="s">
         <v>257</v>
       </c>
-      <c r="B49" s="196"/>
+      <c r="B49" s="202"/>
       <c r="C49" s="54"/>
       <c r="D49" s="181">
         <v>110000</v>
@@ -2723,10 +2737,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="190" t="s">
+      <c r="A50" s="195" t="s">
         <v>260</v>
       </c>
-      <c r="B50" s="191"/>
+      <c r="B50" s="196"/>
       <c r="C50" s="54"/>
       <c r="D50" s="181">
         <v>135000</v>
@@ -2749,10 +2763,10 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="190" t="s">
+      <c r="A52" s="195" t="s">
         <v>274</v>
       </c>
-      <c r="B52" s="191"/>
+      <c r="B52" s="196"/>
       <c r="C52" s="54"/>
       <c r="D52" s="181">
         <v>150000</v>
@@ -2762,10 +2776,10 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="192" t="s">
+      <c r="A53" s="198" t="s">
         <v>270</v>
       </c>
-      <c r="B53" s="193"/>
+      <c r="B53" s="199"/>
       <c r="C53" s="5"/>
       <c r="D53" s="181">
         <v>110000</v>
@@ -2775,10 +2789,10 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="190" t="s">
+      <c r="A54" s="195" t="s">
         <v>259</v>
       </c>
-      <c r="B54" s="191"/>
+      <c r="B54" s="196"/>
       <c r="C54" s="5"/>
       <c r="D54" s="97">
         <v>51150</v>
@@ -2786,8 +2800,8 @@
       <c r="E54" s="151" t="s">
         <v>256</v>
       </c>
-      <c r="I54" s="190"/>
-      <c r="J54" s="191"/>
+      <c r="I54" s="195"/>
+      <c r="J54" s="196"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="25" t="s">
@@ -2898,10 +2912,10 @@
       <c r="E66" s="111"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="190" t="s">
+      <c r="A67" s="195" t="s">
         <v>279</v>
       </c>
-      <c r="B67" s="191"/>
+      <c r="B67" s="196"/>
       <c r="C67" s="5"/>
       <c r="D67" s="97">
         <f>2*304993.06</f>
@@ -2931,12 +2945,12 @@
     <row r="70" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="72" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="197" t="s">
+      <c r="A72" s="203" t="s">
         <v>43</v>
       </c>
-      <c r="B72" s="198"/>
-      <c r="C72" s="198"/>
-      <c r="D72" s="199"/>
+      <c r="B72" s="189"/>
+      <c r="C72" s="189"/>
+      <c r="D72" s="190"/>
       <c r="E72" s="144"/>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3102,16 +3116,16 @@
       <c r="F92" s="123"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="194" t="s">
+      <c r="A93" s="200" t="s">
         <v>58</v>
       </c>
-      <c r="B93" s="189"/>
-      <c r="C93" s="189"/>
+      <c r="B93" s="192"/>
+      <c r="C93" s="192"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="189"/>
-      <c r="B94" s="189"/>
-      <c r="C94" s="189"/>
+      <c r="A94" s="192"/>
+      <c r="B94" s="192"/>
+      <c r="C94" s="192"/>
     </row>
     <row r="95" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="53"/>
@@ -3146,40 +3160,35 @@
       <c r="M99" s="7"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="188"/>
-      <c r="B100" s="189"/>
-      <c r="C100" s="189"/>
-      <c r="D100" s="189"/>
-      <c r="E100" s="189"/>
+      <c r="A100" s="197"/>
+      <c r="B100" s="192"/>
+      <c r="C100" s="192"/>
+      <c r="D100" s="192"/>
+      <c r="E100" s="192"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="189"/>
-      <c r="B101" s="189"/>
-      <c r="C101" s="189"/>
-      <c r="D101" s="189"/>
-      <c r="E101" s="189"/>
+      <c r="A101" s="192"/>
+      <c r="B101" s="192"/>
+      <c r="C101" s="192"/>
+      <c r="D101" s="192"/>
+      <c r="E101" s="192"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="189"/>
-      <c r="B102" s="189"/>
-      <c r="C102" s="189"/>
-      <c r="D102" s="189"/>
-      <c r="E102" s="189"/>
+      <c r="A102" s="192"/>
+      <c r="B102" s="192"/>
+      <c r="C102" s="192"/>
+      <c r="D102" s="192"/>
+      <c r="E102" s="192"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="189"/>
-      <c r="B103" s="189"/>
-      <c r="C103" s="189"/>
-      <c r="D103" s="189"/>
-      <c r="E103" s="189"/>
+      <c r="A103" s="192"/>
+      <c r="B103" s="192"/>
+      <c r="C103" s="192"/>
+      <c r="D103" s="192"/>
+      <c r="E103" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="A52:B52"/>
@@ -3193,6 +3202,11 @@
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A54:B54"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3231,10 +3245,10 @@
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="216">
+      <c r="F1" s="209">
         <v>1241030.1599999999</v>
       </c>
-      <c r="G1" s="214"/>
+      <c r="G1" s="206"/>
       <c r="H1" s="185"/>
       <c r="I1" s="185"/>
       <c r="J1" s="185"/>
@@ -3242,16 +3256,16 @@
         <v>60</v>
       </c>
       <c r="L1" s="185"/>
-      <c r="M1" s="213">
+      <c r="M1" s="205">
         <f>P1</f>
         <v>3600000</v>
       </c>
-      <c r="N1" s="214"/>
+      <c r="N1" s="206"/>
       <c r="O1" s="138"/>
-      <c r="P1" s="212">
+      <c r="P1" s="204">
         <v>3600000</v>
       </c>
-      <c r="Q1" s="189"/>
+      <c r="Q1" s="192"/>
       <c r="R1" s="19"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3262,104 +3276,104 @@
       <c r="E2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="204">
+      <c r="F2" s="220">
         <v>561462.80000000005</v>
       </c>
-      <c r="G2" s="205"/>
+      <c r="G2" s="208"/>
       <c r="H2" s="185" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="215">
+      <c r="I2" s="207">
         <v>1200000</v>
       </c>
-      <c r="J2" s="205"/>
+      <c r="J2" s="208"/>
       <c r="K2" s="185" t="s">
         <v>63</v>
       </c>
       <c r="L2" s="185"/>
-      <c r="M2" s="215">
+      <c r="M2" s="207">
         <f>2*304993.06</f>
         <v>609986.12</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="208"/>
       <c r="O2" s="140"/>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="221"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="216"/>
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="217" t="s">
+      <c r="A3" s="210" t="s">
         <v>64</v>
       </c>
       <c r="B3" s="117"/>
-      <c r="C3" s="206" t="s">
+      <c r="C3" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="206" t="s">
+      <c r="D3" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="211" t="s">
+      <c r="E3" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="206" t="s">
+      <c r="F3" s="217" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="208" t="s">
+      <c r="G3" s="212" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="206" t="s">
+      <c r="H3" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="219" t="s">
+      <c r="I3" s="214" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="208" t="s">
+      <c r="J3" s="212" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="210" t="str">
+      <c r="K3" s="221" t="str">
         <f>K2</f>
         <v>Plan de pago metrogas:</v>
       </c>
-      <c r="L3" s="208" t="s">
+      <c r="L3" s="212" t="s">
         <v>72</v>
       </c>
-      <c r="M3" s="208" t="s">
+      <c r="M3" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="208" t="s">
+      <c r="N3" s="212" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="208" t="s">
+      <c r="O3" s="212" t="s">
         <v>75</v>
       </c>
       <c r="P3" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="222" t="s">
+      <c r="Q3" s="219" t="s">
         <v>77</v>
       </c>
       <c r="T3" s="44"/>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="218"/>
+      <c r="A4" s="211"/>
       <c r="B4" s="118"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="209"/>
-      <c r="H4" s="207"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="207"/>
-      <c r="L4" s="209"/>
-      <c r="M4" s="209"/>
-      <c r="N4" s="209"/>
-      <c r="O4" s="209"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
       <c r="P4" s="58" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="Q4" s="207"/>
+      <c r="Q4" s="218"/>
     </row>
     <row r="5" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="61"/>
@@ -7474,7 +7488,7 @@
       <c r="D68" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="E68" s="60"/>
+      <c r="E68" s="224"/>
       <c r="F68" s="76">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -9007,100 +9021,107 @@
       <c r="H94" s="120"/>
     </row>
     <row r="95" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D95" s="188" t="str">
+      <c r="D95" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, LES PEDIMOS ENCARECIDAMENTE QUE RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. IMPORTANTE PARA DUEÑOS O INQUILINOS DE DEPARTAMENTOS O COCHERAS: QUEREMOS RECORDARLES UNA CUESTIÓN IMPORTANTE RESPECTO A LOS PAGOS DE EXPENSAS, QUE AYUDA A EVITAR ERRORES EN LA IMPUTACIÓN DE LOS MISMOS. EL SISTEMA QUE UTILIZAMOS ASIGNA CENTAVOS ÚNICOS A CADA UNIDAD FUNCIONAL (UF), LO CUAL NOS PERMITE IDENTIFICAR AUTOMÁTICAMENTE A QUÉ UNIDAD CORRESPONDE CADA TRANSFERENCIA. ES DECIR, CADA UF TIENE UN NÚMERO ESPECÍFICO DE CENTAVOS QUE ACTÚA COMO "IDENTIFICADOR". POR EJEMPLO, SI TU UF ES LA 45, EL IMPORTE A ABONAR DEBERÍA TERMINAR EN $...,45. SI TENÉS MÁS DE UNA UNIDAD (POR EJEMPLO, UN DEPARTAMENTO Y UNA COCHERA), CADA UNA TIENE SU PROPIO CÓDIGO DE CENTAVOS. EN ESOS CASOS, TE PEDIMOS POR FAVOR QUE REALICES UNA TRANSFERENCIA POR CADA UF, RESPETANDO EL IMPORTE CON SUS CENTAVOS CORRESPONDIENTES. SABEMOS QUE A VECES, POR COMODIDAD, SE SUELE ENVIAR TODO JUNTO EN UNA SOLA TRANSFERENCIA, PERO ESTO PUEDE GENERAR CONFUSIÓN O ERRORES EN LA IMPUTACIÓN AUTOMÁTICA. REALIZAR LOS PAGOS POR SEPARADO NOS PERMITE ASEGURAR QUE CADA IMPORTE SE ASIGNE CORRECTAMENTE. AGRADECEMOS MUCHÍSIMO LA COLABORACIÓN PARA SEGUIR MANTENIENDO TODO ORDENADO. SALUDOS CORDIALES.</v>
       </c>
-      <c r="E95" s="189"/>
-      <c r="F95" s="189"/>
-      <c r="G95" s="189"/>
-      <c r="H95" s="189"/>
-      <c r="I95" s="189"/>
-      <c r="J95" s="189"/>
-      <c r="K95" s="189"/>
-      <c r="L95" s="189"/>
-      <c r="M95" s="189"/>
-      <c r="N95" s="189"/>
-      <c r="O95" s="189"/>
-      <c r="P95" s="189"/>
+      <c r="E95" s="192"/>
+      <c r="F95" s="192"/>
+      <c r="G95" s="192"/>
+      <c r="H95" s="192"/>
+      <c r="I95" s="192"/>
+      <c r="J95" s="192"/>
+      <c r="K95" s="192"/>
+      <c r="L95" s="192"/>
+      <c r="M95" s="192"/>
+      <c r="N95" s="192"/>
+      <c r="O95" s="192"/>
+      <c r="P95" s="192"/>
     </row>
     <row r="96" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D96" s="189"/>
-      <c r="E96" s="189"/>
-      <c r="F96" s="189"/>
-      <c r="G96" s="189"/>
-      <c r="H96" s="189"/>
-      <c r="I96" s="189"/>
-      <c r="J96" s="189"/>
-      <c r="K96" s="189"/>
-      <c r="L96" s="189"/>
-      <c r="M96" s="189"/>
-      <c r="N96" s="189"/>
-      <c r="O96" s="189"/>
-      <c r="P96" s="189"/>
+      <c r="D96" s="192"/>
+      <c r="E96" s="192"/>
+      <c r="F96" s="192"/>
+      <c r="G96" s="192"/>
+      <c r="H96" s="192"/>
+      <c r="I96" s="192"/>
+      <c r="J96" s="192"/>
+      <c r="K96" s="192"/>
+      <c r="L96" s="192"/>
+      <c r="M96" s="192"/>
+      <c r="N96" s="192"/>
+      <c r="O96" s="192"/>
+      <c r="P96" s="192"/>
     </row>
     <row r="97" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D97" s="189"/>
-      <c r="E97" s="189"/>
-      <c r="F97" s="189"/>
-      <c r="G97" s="189"/>
-      <c r="H97" s="189"/>
-      <c r="I97" s="189"/>
-      <c r="J97" s="189"/>
-      <c r="K97" s="189"/>
-      <c r="L97" s="189"/>
-      <c r="M97" s="189"/>
-      <c r="N97" s="189"/>
-      <c r="O97" s="189"/>
-      <c r="P97" s="189"/>
+      <c r="D97" s="192"/>
+      <c r="E97" s="192"/>
+      <c r="F97" s="192"/>
+      <c r="G97" s="192"/>
+      <c r="H97" s="192"/>
+      <c r="I97" s="192"/>
+      <c r="J97" s="192"/>
+      <c r="K97" s="192"/>
+      <c r="L97" s="192"/>
+      <c r="M97" s="192"/>
+      <c r="N97" s="192"/>
+      <c r="O97" s="192"/>
+      <c r="P97" s="192"/>
     </row>
     <row r="98" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="189"/>
-      <c r="E98" s="189"/>
-      <c r="F98" s="189"/>
-      <c r="G98" s="189"/>
-      <c r="H98" s="189"/>
-      <c r="I98" s="189"/>
-      <c r="J98" s="189"/>
-      <c r="K98" s="189"/>
-      <c r="L98" s="189"/>
-      <c r="M98" s="189"/>
-      <c r="N98" s="189"/>
-      <c r="O98" s="189"/>
-      <c r="P98" s="189"/>
+      <c r="D98" s="192"/>
+      <c r="E98" s="192"/>
+      <c r="F98" s="192"/>
+      <c r="G98" s="192"/>
+      <c r="H98" s="192"/>
+      <c r="I98" s="192"/>
+      <c r="J98" s="192"/>
+      <c r="K98" s="192"/>
+      <c r="L98" s="192"/>
+      <c r="M98" s="192"/>
+      <c r="N98" s="192"/>
+      <c r="O98" s="192"/>
+      <c r="P98" s="192"/>
     </row>
     <row r="99" spans="4:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="189"/>
-      <c r="E99" s="189"/>
-      <c r="F99" s="189"/>
-      <c r="G99" s="189"/>
-      <c r="H99" s="189"/>
-      <c r="I99" s="189"/>
-      <c r="J99" s="189"/>
-      <c r="K99" s="189"/>
-      <c r="L99" s="189"/>
-      <c r="M99" s="189"/>
-      <c r="N99" s="189"/>
-      <c r="O99" s="189"/>
-      <c r="P99" s="189"/>
+      <c r="D99" s="192"/>
+      <c r="E99" s="192"/>
+      <c r="F99" s="192"/>
+      <c r="G99" s="192"/>
+      <c r="H99" s="192"/>
+      <c r="I99" s="192"/>
+      <c r="J99" s="192"/>
+      <c r="K99" s="192"/>
+      <c r="L99" s="192"/>
+      <c r="M99" s="192"/>
+      <c r="N99" s="192"/>
+      <c r="O99" s="192"/>
+      <c r="P99" s="192"/>
     </row>
     <row r="100" spans="4:16" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D100" s="189"/>
-      <c r="E100" s="189"/>
-      <c r="F100" s="189"/>
-      <c r="G100" s="189"/>
-      <c r="H100" s="189"/>
-      <c r="I100" s="189"/>
-      <c r="J100" s="189"/>
-      <c r="K100" s="189"/>
-      <c r="L100" s="189"/>
-      <c r="M100" s="189"/>
-      <c r="N100" s="189"/>
-      <c r="O100" s="189"/>
-      <c r="P100" s="189"/>
+      <c r="D100" s="192"/>
+      <c r="E100" s="192"/>
+      <c r="F100" s="192"/>
+      <c r="G100" s="192"/>
+      <c r="H100" s="192"/>
+      <c r="I100" s="192"/>
+      <c r="J100" s="192"/>
+      <c r="K100" s="192"/>
+      <c r="L100" s="192"/>
+      <c r="M100" s="192"/>
+      <c r="N100" s="192"/>
+      <c r="O100" s="192"/>
+      <c r="P100" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D95:P100"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
@@ -9117,13 +9138,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D95:P100"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9163,7 +9177,9 @@
       <c r="D11" s="120"/>
     </row>
     <row r="12" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D12" s="120"/>
+      <c r="D12" s="120" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="13" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D13" s="120"/>
@@ -9172,7 +9188,9 @@
       <c r="D14" s="120"/>
     </row>
     <row r="15" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="120"/>
+      <c r="D15" s="223" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="177" t="s">
